--- a/output/pdf_financials_xlsx/ET.xlsx
+++ b/output/pdf_financials_xlsx/ET.xlsx
@@ -6302,55 +6302,55 @@
         <v>6.769</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>12.828</v>
+        <v>12.183</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>13.762</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>14.32</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>10.727</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>10.217</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>12.418</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>13.835</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.010091</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>7.885</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>8.244999999999999</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>8.279</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>9.513999999999999</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>10.893</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>14.697</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>19.246</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>24.195</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>28.112</v>
       </c>
     </row>
     <row r="93">
@@ -11382,7 +11382,11 @@
           <t>Share based payment reserve</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -19662,7 +19666,11 @@
           <t>w Share based payment reserve</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ET.xlsx
+++ b/output/pdf_financials_xlsx/ET.xlsx
@@ -2585,7 +2585,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>81.376</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>133.755</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>81.376</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>133.755</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>116.217</v>
+        <v>34.841</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>15.124</v>
@@ -26884,7 +26884,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">

--- a/output/pdf_financials_xlsx/ET.xlsx
+++ b/output/pdf_financials_xlsx/ET.xlsx
@@ -2253,49 +2253,49 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1.023</v>
+        <v>8.153</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>1.232</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.428</v>
+        <v>8.279</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.383</v>
+        <v>10.918</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.238</v>
+        <v>11.187</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>10.637</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.010957</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>10.505</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.217</v>
+        <v>10.942</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.432</v>
+        <v>10.68</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.795</v>
+        <v>11.679</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>1.207</v>
+        <v>11.451</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>1.238</v>
+        <v>10.851</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>1.028</v>
+        <v>9.721</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.767</v>
+        <v>10.337</v>
       </c>
       <c r="S28" s="1" t="inlineStr">
         <is>
@@ -2320,49 +2320,49 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>108.289</v>
+        <v>115.419</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>81.157</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>86.89100000000001</v>
+        <v>94.742</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>83.18600000000001</v>
+        <v>93.721</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>88.827</v>
+        <v>99.776</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>96.023</v>
+        <v>106.66</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.092225</v>
+        <v>0.103182</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>72.185</v>
+        <v>82.69</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>103.91</v>
+        <v>114.635</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>91.31399999999999</v>
+        <v>101.562</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>55.953</v>
+        <v>66.837</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>98.81</v>
+        <v>109.054</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>88.672</v>
+        <v>98.285</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>96.72499999999999</v>
+        <v>105.418</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>79.892</v>
+        <v>89.462</v>
       </c>
       <c r="S29" s="1" t="inlineStr">
         <is>
@@ -2387,49 +2387,49 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>35.01563414484299</v>
+        <v>37.32114505964256</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>27.66087252897069</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>27.47063751758587</v>
+        <v>29.9527354926416</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>25.55449060591539</v>
+        <v>28.7908111229894</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>24.42946486031584</v>
+        <v>27.44069129772336</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>25.16655746297995</v>
+        <v>27.95439654042721</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.02398993840263038</v>
+        <v>0.02684011736796104</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>17.91938078404893</v>
+        <v>20.52716765301664</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>23.42657973288604</v>
+        <v>25.84453823192562</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>20.91517938945285</v>
+        <v>23.26245098398505</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>16.31815636592707</v>
+        <v>19.4923706866382</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>22.40508280878698</v>
+        <v>24.72790102853411</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>19.50644333865695</v>
+        <v>21.62115192552213</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>18.79556795746732</v>
+        <v>20.48478865795078</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>15.92670192554967</v>
+        <v>17.83450918319136</v>
       </c>
       <c r="S30" s="1" t="inlineStr">
         <is>
@@ -6779,49 +6779,49 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>8.153</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>1.232</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>8.279</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>10.918</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>11.187</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>10.637</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.010957</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>10.505</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>10.942</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>10.68</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>11.679</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>11.451</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>10.851</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>9.721</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>10.337</v>
       </c>
       <c r="S100" s="1" t="inlineStr">
         <is>
@@ -7583,49 +7583,49 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.795</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.187</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.187</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.169</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>9.000000000000001e-05</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>6.549</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.181</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.257</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.515</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>1.016</v>
       </c>
       <c r="S112" s="1" t="inlineStr">
         <is>
@@ -29732,7 +29732,11 @@
           <t>Depreciation of property, plant and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -31146,7 +31150,11 @@
           <t>Proceeds from disposal of property, plant and equipment (note 5)</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -32680,7 +32688,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -37514,7 +37526,11 @@
           <t>Depreciation of property, plant and equipment QRWH</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -38146,7 +38162,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -38676,7 +38696,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -40016,7 +40040,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
